--- a/artfynd/A 33150-2021 artfynd.xlsx
+++ b/artfynd/A 33150-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33150-2021 artfynd.xlsx
+++ b/artfynd/A 33150-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>77888162</v>
       </c>
       <c r="B2" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620578.3040295431</v>
+        <v>620578</v>
       </c>
       <c r="R2" t="n">
-        <v>6658944.985674097</v>
+        <v>6658945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2019-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -826,6 +811,231 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124725847</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjömossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>620740</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6658893</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Claus Rüffler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Claus Rüffler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>78354489</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörbo, 1,4 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>620708</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6658841</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-05-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
